--- a/Result/profitability/3587.xlsx
+++ b/Result/profitability/3587.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.725</v>
+        <v>1.46625</v>
       </c>
       <c r="N2" t="n">
-        <v>32.0025</v>
+        <v>31.69125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>1.45</v>
+        <v>1.285</v>
       </c>
       <c r="N3" t="n">
-        <v>33.0475</v>
+        <v>33.72750000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.22625</v>
+        <v>1.23125</v>
       </c>
       <c r="N4" t="n">
-        <v>33.945</v>
+        <v>35.14125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.0775</v>
       </c>
       <c r="N5" t="n">
-        <v>35.36125</v>
+        <v>36.13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9324999999999999</v>
+        <v>0.76875</v>
       </c>
       <c r="N6" t="n">
-        <v>33.42125</v>
+        <v>33.73375000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="N7" t="n">
-        <v>32.74125</v>
+        <v>33.22</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4275</v>
+        <v>0.2475</v>
       </c>
       <c r="N8" t="n">
-        <v>32.4425</v>
+        <v>32.8125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1644</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1087</v>
+      </c>
+      <c r="E75" t="n">
+        <v>556</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="G75" t="n">
+        <v>272</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>290</v>
+      </c>
+      <c r="K75" t="n">
+        <v>57</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.765</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.355</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6428571428571428</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.960000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09582389122693424</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.5799999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4202898550724636</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.150000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2220216606498195</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
